--- a/data/export/2026-09-15-浦东35路.xlsx
+++ b/data/export/2026-09-15-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,18 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,7 +3060,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,22 +3175,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,22 +3294,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,22 +4000,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4130,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4318,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,22 +4361,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,22 +4480,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4595,17 +4599,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4675,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4724,7 +4728,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4794,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4833,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,22 +4956,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,22 +5075,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,22 +5194,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5305,22 +5309,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,14 +5424,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -5435,7 +5439,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,22 +5543,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5654,7 +5658,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5734,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5773,7 +5777,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5853,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,14 +5896,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -5907,7 +5911,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6011,7 +6015,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6091,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6130,22 +6134,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6368,22 +6372,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6498,7 +6502,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6602,22 +6606,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6731,7 +6735,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6801,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,17 +6844,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7047,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7086,22 +7090,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7205,22 +7209,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7324,22 +7328,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7443,7 +7447,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7523,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7562,14 +7566,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -7577,7 +7581,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7681,7 +7685,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7761,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7800,14 +7804,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -7815,7 +7819,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7938,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7972,12 +7976,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -7999,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8038,22 +8042,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8090,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -8103,10 +8107,14 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:01采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8114,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,12 +8146,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8168,7 +8176,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8201,29 +8209,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:01采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8233,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,12 +8265,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8272,22 +8280,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8320,24 +8328,24 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:01采样：该车到重点站浦建路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -8352,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8376,12 +8384,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8401,7 +8409,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8439,29 +8447,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8471,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8495,12 +8503,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8510,22 +8518,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8563,19 +8571,19 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：17:50采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
@@ -8586,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8610,37 +8618,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8668,12 +8676,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8701,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8709,10 +8717,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±4分钟；反向重点站锦绣路花木路 ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8730,7 +8754,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8784,27 +8808,31 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8812,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8836,37 +8864,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8899,27 +8927,31 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8927,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8951,33 +8983,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9015,19 +9051,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：18:01采样，终点ETA 27分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
@@ -9038,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9062,37 +9098,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9130,19 +9166,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：18:01采样，终点ETA 19分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
@@ -9153,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9177,37 +9213,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9351,27 +9387,31 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9379,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9403,37 +9443,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9466,27 +9506,31 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -9494,7 +9538,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9518,37 +9562,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9581,27 +9625,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9609,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9633,37 +9681,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9671,24 +9719,24 @@
       <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9696,35 +9744,39 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9738,47 +9790,3299 @@
       <c r="T79" s="2" t="inlineStr"/>
       <c r="U79" s="2" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="V79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W79" s="2" t="inlineStr">
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>149.3</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>143.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：19:31采样，终点ETA 34分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X79" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y79" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z79" s="2" t="inlineStr">
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr">
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>153.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>149.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
         </is>
       </c>
     </row>
